--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484622_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484622_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.589700000000001</v>
+        <v>8.3866</v>
       </c>
       <c r="E2" t="n">
-        <v>6.0356</v>
+        <v>5.8572</v>
       </c>
       <c r="F2" t="n">
-        <v>2.5542</v>
+        <v>2.5294</v>
       </c>
       <c r="G2" t="n">
         <v>5.0385</v>
@@ -610,13 +610,13 @@
         <v>4.0317</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6796</v>
+        <v>0.4764</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2346</v>
+        <v>0.0562</v>
       </c>
       <c r="U2" t="n">
-        <v>0.445</v>
+        <v>0.4202</v>
       </c>
       <c r="V2" t="n">
         <v>1.5889</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>L. GARCIA JIMENEZ</t>
+          <t>J. TALLON GUIA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.883</v>
+        <v>1.7809</v>
       </c>
       <c r="E3" t="n">
-        <v>2.8971</v>
+        <v>0.2401</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.0141</v>
+        <v>1.5409</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7472</v>
+        <v>0.4135</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.4515</v>
+        <v>0.9136</v>
       </c>
       <c r="I3" t="n">
-        <v>1.1987</v>
+        <v>-0.5001</v>
       </c>
       <c r="J3" t="n">
-        <v>3.2999</v>
+        <v>1.452</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0493</v>
+        <v>0.7337</v>
       </c>
       <c r="L3" t="n">
-        <v>3.2506</v>
+        <v>0.7183</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.5526</v>
+        <v>-1.0385</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.5008</v>
+        <v>0.1799</v>
       </c>
       <c r="O3" t="n">
-        <v>-2.0519</v>
+        <v>-1.2184</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.5656</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.8326</v>
+        <v>-0.9163</v>
       </c>
       <c r="R3" t="n">
-        <v>1.8326</v>
+        <v>3.4819</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8243</v>
+        <v>0.0688</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4744</v>
+        <v>-0.2956</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3499</v>
+        <v>0.3644</v>
       </c>
       <c r="V3" t="n">
-        <v>0.3115</v>
+        <v>-1.267</v>
       </c>
       <c r="W3" t="n">
-        <v>0.9554</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.6439</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. TALLON GUIA</t>
+          <t>L. GARCIA JIMENEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.5092</v>
+        <v>1.5946</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.2546</v>
+        <v>2.6087</v>
       </c>
       <c r="F4" t="n">
-        <v>1.7638</v>
+        <v>-1.0141</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4135</v>
+        <v>0.7472</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9136</v>
+        <v>-0.4515</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.5001</v>
+        <v>1.1987</v>
       </c>
       <c r="J4" t="n">
-        <v>1.452</v>
+        <v>3.2999</v>
       </c>
       <c r="K4" t="n">
-        <v>0.7337</v>
+        <v>0.0493</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7183</v>
+        <v>3.2506</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.0385</v>
+        <v>-2.5526</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1799</v>
+        <v>-0.5008</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.2184</v>
+        <v>-2.0519</v>
       </c>
       <c r="P4" t="n">
-        <v>2.5656</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9163</v>
+        <v>-1.8326</v>
       </c>
       <c r="R4" t="n">
-        <v>3.4819</v>
+        <v>1.8326</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2029</v>
+        <v>0.5358000000000001</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.7903</v>
+        <v>0.1859</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5874</v>
+        <v>0.3499</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.267</v>
+        <v>0.3115</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>0.9554</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.267</v>
+        <v>-0.6439</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7304</v>
+        <v>0.7968</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.1732</v>
+        <v>-1.2554</v>
       </c>
       <c r="F5" t="n">
-        <v>1.9036</v>
+        <v>2.0522</v>
       </c>
       <c r="G5" t="n">
         <v>1.65</v>
@@ -844,13 +844,13 @@
         <v>3.2986</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3736</v>
+        <v>0.44</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2542</v>
+        <v>0.172</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1194</v>
+        <v>0.2681</v>
       </c>
       <c r="V5" t="n">
         <v>-0.0104</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4925</v>
+        <v>0.1297</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1394</v>
+        <v>-0.4279</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6319</v>
+        <v>0.5576</v>
       </c>
       <c r="G7" t="n">
         <v>-0.4474</v>
@@ -1000,13 +1000,13 @@
         <v>0.3665</v>
       </c>
       <c r="S7" t="n">
-        <v>0.5734</v>
+        <v>0.2106</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4759</v>
+        <v>0.1874</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0975</v>
+        <v>0.0232</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.4078</v>
+        <v>-0.1164</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.0814</v>
+        <v>-0.8891</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6736</v>
+        <v>0.7727000000000001</v>
       </c>
       <c r="G8" t="n">
         <v>0.6807</v>
@@ -1078,13 +1078,13 @@
         <v>0.1833</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3555</v>
+        <v>-0.0641</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1652</v>
+        <v>0.0272</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1903</v>
+        <v>-0.09130000000000001</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. LARA BARRACHINA</t>
+          <t>B. KABASELE KATUMBA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.6451</v>
+        <v>-0.5169</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.0237</v>
+        <v>0.1881</v>
       </c>
       <c r="F9" t="n">
-        <v>1.3786</v>
+        <v>-0.705</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.4419</v>
+        <v>-1.68</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.7331</v>
+        <v>1.0256</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.7088</v>
+        <v>-2.7056</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.4083</v>
+        <v>0.1018</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.5333</v>
+        <v>0.6594</v>
       </c>
       <c r="L9" t="n">
-        <v>0.125</v>
+        <v>-0.5577</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.0336</v>
+        <v>-1.7818</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.1999</v>
+        <v>0.3662</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.8338</v>
+        <v>-2.148</v>
       </c>
       <c r="P9" t="n">
-        <v>2.0158</v>
+        <v>1.0995</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.9321</v>
+        <v>1.0995</v>
       </c>
       <c r="S9" t="n">
-        <v>0.7259</v>
+        <v>0.3855</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0761</v>
+        <v>0.0864</v>
       </c>
       <c r="U9" t="n">
-        <v>0.8021</v>
+        <v>0.2992</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.945</v>
+        <v>-0.3219</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.6231</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
         <v>-0.3219</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>B. KABASELE KATUMBA</t>
+          <t>M. LARA BARRACHINA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.0283</v>
+        <v>-1.1237</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.1004</v>
+        <v>-2.106</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.9278999999999999</v>
+        <v>0.9822</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.68</v>
+        <v>-2.4419</v>
       </c>
       <c r="H10" t="n">
-        <v>1.0256</v>
+        <v>-1.7331</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.7056</v>
+        <v>-0.7088</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1018</v>
+        <v>-0.4083</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6594</v>
+        <v>-0.5333</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.5577</v>
+        <v>0.125</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.7818</v>
+        <v>-2.0336</v>
       </c>
       <c r="N10" t="n">
-        <v>0.3662</v>
+        <v>-1.1999</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.148</v>
+        <v>-0.8338</v>
       </c>
       <c r="P10" t="n">
-        <v>1.0995</v>
+        <v>2.0158</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R10" t="n">
-        <v>1.0995</v>
+        <v>2.9321</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1259</v>
+        <v>0.2474</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2021</v>
+        <v>-0.1583</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0762</v>
+        <v>0.4057</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.3219</v>
+        <v>-0.945</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>-0.6231</v>
       </c>
       <c r="X10" t="n">
         <v>-0.3219</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>P. BALAGUER BARBA</t>
+          <t>M. CALANCHE GONZALEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.063</v>
+        <v>-2.0271</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.5023</v>
+        <v>-4.7248</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.5608</v>
+        <v>2.6977</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.5169</v>
+        <v>-1.1409</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.3053</v>
+        <v>-0.6249</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.2116</v>
+        <v>-0.516</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.9231</v>
+        <v>-1.9314</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>-0.7743</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.9231</v>
+        <v>-1.157</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.5938</v>
+        <v>0.7905</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.3053</v>
+        <v>0.1495</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.2885</v>
+        <v>0.641</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>-1.8326</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-3.6651</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.8326</v>
       </c>
       <c r="S11" t="n">
-        <v>0.4539</v>
+        <v>-0.0091</v>
       </c>
       <c r="T11" t="n">
-        <v>0.4208</v>
+        <v>-0.0837</v>
       </c>
       <c r="U11" t="n">
-        <v>0.033</v>
+        <v>0.0746</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.9554</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.9554</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>M. CALANCHE GONZALEZ</t>
+          <t>P. BALAGUER BARBA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,64 +1345,64 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.8132</v>
+        <v>-2.3981</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.4118</v>
+        <v>-1.8869</v>
       </c>
       <c r="F12" t="n">
-        <v>2.5986</v>
+        <v>-0.5112</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.1409</v>
+        <v>-2.5169</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.6249</v>
+        <v>-0.3053</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.516</v>
+        <v>-2.2116</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.9314</v>
+        <v>-1.9231</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.7743</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.157</v>
+        <v>-1.9231</v>
       </c>
       <c r="M12" t="n">
-        <v>0.7905</v>
+        <v>-0.5938</v>
       </c>
       <c r="N12" t="n">
-        <v>0.1495</v>
+        <v>-0.3053</v>
       </c>
       <c r="O12" t="n">
-        <v>0.641</v>
+        <v>-0.2885</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.8326</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>-3.6651</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.8326</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7952</v>
+        <v>0.1188</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7707000000000001</v>
+        <v>0.0362</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0244</v>
+        <v>0.08260000000000001</v>
       </c>
       <c r="V12" t="n">
-        <v>0.9554</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>0.9554</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.2677</v>
+        <v>-3.9763</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.6457</v>
+        <v>-4.4534</v>
       </c>
       <c r="F13" t="n">
-        <v>0.378</v>
+        <v>0.4771</v>
       </c>
       <c r="G13" t="n">
         <v>-2.9588</v>
@@ -1468,13 +1468,13 @@
         <v>1.0995</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.8691</v>
+        <v>-0.5777</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6056</v>
+        <v>-0.4133</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2635</v>
+        <v>-0.1644</v>
       </c>
       <c r="V13" t="n">
         <v>-0.6231</v>
@@ -1501,43 +1501,43 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.604799999999999</v>
+        <v>3.155200000000002</v>
       </c>
       <c r="E14" t="n">
-        <v>-6.774699999999998</v>
+        <v>-6.2243</v>
       </c>
       <c r="F14" t="n">
         <v>9.379499999999998</v>
       </c>
       <c r="G14" t="n">
-        <v>-2.0309</v>
+        <v>-2.030900000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>6.944799999999999</v>
+        <v>6.944799999999997</v>
       </c>
       <c r="I14" t="n">
         <v>-8.9758</v>
       </c>
       <c r="J14" t="n">
-        <v>7.5814</v>
+        <v>7.581399999999999</v>
       </c>
       <c r="K14" t="n">
         <v>8.060399999999998</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.4788999999999999</v>
+        <v>-0.4789000000000003</v>
       </c>
       <c r="M14" t="n">
-        <v>-9.612400000000001</v>
+        <v>-9.612399999999999</v>
       </c>
       <c r="N14" t="n">
         <v>-1.1155</v>
       </c>
       <c r="O14" t="n">
-        <v>-8.4971</v>
+        <v>-8.497099999999998</v>
       </c>
       <c r="P14" t="n">
-        <v>3.6651</v>
+        <v>3.665099999999999</v>
       </c>
       <c r="Q14" t="n">
         <v>-16.4932</v>
@@ -1546,13 +1546,13 @@
         <v>20.1583</v>
       </c>
       <c r="S14" t="n">
-        <v>1.2821</v>
+        <v>1.832399999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.7501000000000002</v>
+        <v>-0.1995999999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>2.0323</v>
+        <v>2.0322</v>
       </c>
       <c r="V14" t="n">
         <v>-0.3115999999999999</v>
@@ -1561,7 +1561,7 @@
         <v>2.887</v>
       </c>
       <c r="X14" t="n">
-        <v>-3.198599999999999</v>
+        <v>-3.1986</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.2611</v>
+        <v>4.5991</v>
       </c>
       <c r="E15" t="n">
-        <v>2.1567</v>
+        <v>2.4452</v>
       </c>
       <c r="F15" t="n">
-        <v>2.1044</v>
+        <v>2.1539</v>
       </c>
       <c r="G15" t="n">
         <v>3.1987</v>
@@ -1624,13 +1624,13 @@
         <v>1.0995</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.07630000000000001</v>
+        <v>0.2617</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.129</v>
+        <v>0.1595</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0526</v>
+        <v>0.1022</v>
       </c>
       <c r="V15" t="n">
         <v>0.9554</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.1582</v>
+        <v>2.1057</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.8115</v>
+        <v>-0.7153</v>
       </c>
       <c r="F16" t="n">
-        <v>2.9697</v>
+        <v>2.821</v>
       </c>
       <c r="G16" t="n">
         <v>0.3507</v>
@@ -1702,13 +1702,13 @@
         <v>1.0995</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0849</v>
+        <v>0.0324</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2572</v>
+        <v>-0.161</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3421</v>
+        <v>0.1934</v>
       </c>
       <c r="V16" t="n">
         <v>0.6231</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. MICHAEL KING</t>
+          <t>L. SALVADOR MONTANES</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.7786</v>
+        <v>1.0435</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.7929</v>
+        <v>2.2357</v>
       </c>
       <c r="F19" t="n">
-        <v>2.5716</v>
+        <v>-1.1922</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4074</v>
+        <v>0.5078</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.6373</v>
+        <v>0.4727</v>
       </c>
       <c r="I19" t="n">
-        <v>1.0447</v>
+        <v>0.035</v>
       </c>
       <c r="J19" t="n">
-        <v>0.5819</v>
+        <v>2.2391</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.3349</v>
+        <v>1.9474</v>
       </c>
       <c r="L19" t="n">
-        <v>0.9167999999999999</v>
+        <v>0.2917</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.1745</v>
+        <v>-1.7314</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.3024</v>
+        <v>-1.4747</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1279</v>
+        <v>-0.2567</v>
       </c>
       <c r="P19" t="n">
-        <v>-2.1991</v>
+        <v>1.2828</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.8484</v>
+        <v>-1.0995</v>
       </c>
       <c r="R19" t="n">
-        <v>1.6493</v>
+        <v>2.3823</v>
       </c>
       <c r="S19" t="n">
-        <v>2.2588</v>
+        <v>-0.4355</v>
       </c>
       <c r="T19" t="n">
-        <v>1.1516</v>
+        <v>-0.4928</v>
       </c>
       <c r="U19" t="n">
-        <v>1.1072</v>
+        <v>0.0573</v>
       </c>
       <c r="V19" t="n">
-        <v>0.3115</v>
+        <v>-0.3115</v>
       </c>
       <c r="W19" t="n">
-        <v>0.3219</v>
+        <v>1.5889</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.0104</v>
+        <v>-1.9005</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>L. SALVADOR MONTANES</t>
+          <t>A. ALVAREZ LENCINA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4228</v>
+        <v>-0.6111</v>
       </c>
       <c r="E20" t="n">
-        <v>2.1396</v>
+        <v>-1.0663</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.7168</v>
+        <v>0.4553</v>
       </c>
       <c r="G20" t="n">
-        <v>0.5078</v>
+        <v>-1.3758</v>
       </c>
       <c r="H20" t="n">
-        <v>0.4727</v>
+        <v>-0.4335</v>
       </c>
       <c r="I20" t="n">
-        <v>0.035</v>
+        <v>-0.9423</v>
       </c>
       <c r="J20" t="n">
-        <v>2.2391</v>
+        <v>-1.1987</v>
       </c>
       <c r="K20" t="n">
-        <v>1.9474</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0.2917</v>
+        <v>-1.1987</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.7314</v>
+        <v>-0.1771</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.4747</v>
+        <v>-0.4335</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.2567</v>
+        <v>0.2564</v>
       </c>
       <c r="P20" t="n">
-        <v>1.2828</v>
+        <v>0.5498</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.0995</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.3823</v>
+        <v>0.5498</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.0562</v>
+        <v>0.2149</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.589</v>
+        <v>0.1324</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4673</v>
+        <v>0.08260000000000001</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.3115</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.5889</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.9005</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. ALVAREZ LENCINA</t>
+          <t>D. MICHAEL KING</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3722</v>
+        <v>-0.6318</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.7779</v>
+        <v>-2.6583</v>
       </c>
       <c r="F21" t="n">
-        <v>0.4057</v>
+        <v>2.0266</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.3758</v>
+        <v>0.4074</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.4335</v>
+        <v>-0.6373</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.9423</v>
+        <v>1.0447</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.1987</v>
+        <v>0.5819</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>-0.3349</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.1987</v>
+        <v>0.9167999999999999</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.1771</v>
+        <v>-0.1745</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.4335</v>
+        <v>-0.3024</v>
       </c>
       <c r="O21" t="n">
-        <v>0.2564</v>
+        <v>0.1279</v>
       </c>
       <c r="P21" t="n">
-        <v>0.5498</v>
+        <v>-2.1991</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-3.8484</v>
       </c>
       <c r="R21" t="n">
-        <v>0.5498</v>
+        <v>1.6493</v>
       </c>
       <c r="S21" t="n">
-        <v>0.4539</v>
+        <v>0.8484</v>
       </c>
       <c r="T21" t="n">
-        <v>0.4208</v>
+        <v>0.2862</v>
       </c>
       <c r="U21" t="n">
-        <v>0.033</v>
+        <v>0.5622</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>0.3115</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.3219</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.0104</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>R. SORO VILLANUEVA</t>
+          <t>E. CIRCUNS RIVERA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.4573</v>
+        <v>-0.9634</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.5281</v>
+        <v>-0.3507</v>
       </c>
       <c r="F22" t="n">
-        <v>1.0708</v>
+        <v>-0.6128</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.4484</v>
+        <v>0.0897</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.6344</v>
+        <v>-2.2218</v>
       </c>
       <c r="I22" t="n">
-        <v>1.186</v>
+        <v>2.3115</v>
       </c>
       <c r="J22" t="n">
-        <v>0.7518</v>
+        <v>1.3141</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.6909</v>
+        <v>-0.8052</v>
       </c>
       <c r="L22" t="n">
-        <v>1.4427</v>
+        <v>2.1193</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.2002</v>
+        <v>-1.2244</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.9434</v>
+        <v>-1.4166</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.2567</v>
+        <v>0.1922</v>
       </c>
       <c r="P22" t="n">
-        <v>-2.1991</v>
+        <v>1.2828</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.8484</v>
+        <v>-1.0995</v>
       </c>
       <c r="R22" t="n">
-        <v>1.6493</v>
+        <v>2.3823</v>
       </c>
       <c r="S22" t="n">
-        <v>0.8682</v>
+        <v>-0.747</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.07539999999999999</v>
+        <v>-0.5652</v>
       </c>
       <c r="U22" t="n">
-        <v>0.9436</v>
+        <v>-0.1818</v>
       </c>
       <c r="V22" t="n">
-        <v>0.3219</v>
+        <v>-1.5889</v>
       </c>
       <c r="W22" t="n">
-        <v>0.6439</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.3219</v>
+        <v>-1.5889</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>E. CIRCUNS RIVERA</t>
+          <t>R. ROMAN MORA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.7706</v>
+        <v>-1.138</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.8314</v>
+        <v>-0.6798</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.9392</v>
+        <v>-0.4583</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0897</v>
+        <v>1.6569</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.2218</v>
+        <v>-1.2829</v>
       </c>
       <c r="I23" t="n">
-        <v>2.3115</v>
+        <v>2.9398</v>
       </c>
       <c r="J23" t="n">
-        <v>1.3141</v>
+        <v>4.0782</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.8052</v>
+        <v>1.2663</v>
       </c>
       <c r="L23" t="n">
-        <v>2.1193</v>
+        <v>2.8119</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.2244</v>
+        <v>-2.4213</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.4166</v>
+        <v>-2.5492</v>
       </c>
       <c r="O23" t="n">
-        <v>0.1922</v>
+        <v>0.1279</v>
       </c>
       <c r="P23" t="n">
-        <v>1.2828</v>
+        <v>-2.0158</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.0995</v>
+        <v>-3.8484</v>
       </c>
       <c r="R23" t="n">
-        <v>2.3823</v>
+        <v>1.8326</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.5541</v>
+        <v>-0.4676</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.046</v>
+        <v>-0.598</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5082</v>
+        <v>0.1304</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.5889</v>
+        <v>-0.3115</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>-0.3115</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.5889</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>R. ROMAN MORA</t>
+          <t>R. SORO VILLANUEVA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.1404</v>
+        <v>-2.0271</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.2567</v>
+        <v>-2.5281</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.8837</v>
+        <v>0.501</v>
       </c>
       <c r="G24" t="n">
-        <v>1.6569</v>
+        <v>-0.4484</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.2829</v>
+        <v>-1.6344</v>
       </c>
       <c r="I24" t="n">
-        <v>2.9398</v>
+        <v>1.186</v>
       </c>
       <c r="J24" t="n">
-        <v>4.0782</v>
+        <v>0.7518</v>
       </c>
       <c r="K24" t="n">
-        <v>1.2663</v>
+        <v>-0.6909</v>
       </c>
       <c r="L24" t="n">
-        <v>2.8119</v>
+        <v>1.4427</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.4213</v>
+        <v>-1.2002</v>
       </c>
       <c r="N24" t="n">
-        <v>-2.5492</v>
+        <v>-0.9434</v>
       </c>
       <c r="O24" t="n">
-        <v>0.1279</v>
+        <v>-0.2567</v>
       </c>
       <c r="P24" t="n">
-        <v>-2.0158</v>
+        <v>-2.1991</v>
       </c>
       <c r="Q24" t="n">
         <v>-3.8484</v>
       </c>
       <c r="R24" t="n">
-        <v>1.8326</v>
+        <v>1.6493</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.47</v>
+        <v>0.2984</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.1749</v>
+        <v>-0.07539999999999999</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.295</v>
+        <v>0.3738</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.3115</v>
+        <v>0.3219</v>
       </c>
       <c r="W24" t="n">
-        <v>-0.3115</v>
+        <v>0.6439</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.5479</v>
+        <v>-2.3176</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.346</v>
+        <v>-3.4422</v>
       </c>
       <c r="F25" t="n">
-        <v>0.7982</v>
+        <v>1.1246</v>
       </c>
       <c r="G25" t="n">
         <v>-1.4515</v>
@@ -2404,13 +2404,13 @@
         <v>2.1991</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.5466</v>
+        <v>-0.3164</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.3137</v>
+        <v>-0.4099</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.2329</v>
+        <v>0.0935</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-5.0627</v>
+        <v>-5.1486</v>
       </c>
       <c r="E26" t="n">
-        <v>-5.4568</v>
+        <v>-5.7452</v>
       </c>
       <c r="F26" t="n">
-        <v>0.3941</v>
+        <v>0.5966</v>
       </c>
       <c r="G26" t="n">
         <v>-4.0301</v>
@@ -2482,13 +2482,13 @@
         <v>1.6493</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.2446</v>
+        <v>-0.3305</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.0196</v>
+        <v>-0.3081</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.225</v>
+        <v>-0.0224</v>
       </c>
       <c r="V26" t="n">
         <v>0.3115</v>
@@ -2515,19 +2515,19 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-2.604900000000001</v>
+        <v>-1.9638</v>
       </c>
       <c r="E27" t="n">
         <v>-9.3795</v>
       </c>
       <c r="F27" t="n">
-        <v>6.774799999999999</v>
+        <v>7.415699999999999</v>
       </c>
       <c r="G27" t="n">
         <v>2.0309</v>
       </c>
       <c r="H27" t="n">
-        <v>-6.9449</v>
+        <v>-6.944899999999999</v>
       </c>
       <c r="I27" t="n">
         <v>8.9758</v>
@@ -2545,7 +2545,7 @@
         <v>-7.5815</v>
       </c>
       <c r="N27" t="n">
-        <v>-8.060499999999999</v>
+        <v>-8.060500000000001</v>
       </c>
       <c r="O27" t="n">
         <v>0.4790000000000001</v>
@@ -2560,16 +2560,16 @@
         <v>16.493</v>
       </c>
       <c r="S27" t="n">
-        <v>-1.282</v>
+        <v>-0.6412</v>
       </c>
       <c r="T27" t="n">
-        <v>-2.0324</v>
+        <v>-2.0323</v>
       </c>
       <c r="U27" t="n">
-        <v>0.7500999999999998</v>
+        <v>1.3912</v>
       </c>
       <c r="V27" t="n">
-        <v>0.3115000000000001</v>
+        <v>0.3114999999999998</v>
       </c>
       <c r="W27" t="n">
         <v>3.1986</v>
